--- a/output/pdf_financials_xlsx/SMP.xlsx
+++ b/output/pdf_financials_xlsx/SMP.xlsx
@@ -1496,19 +1496,19 @@
         <v>0.390818</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.02932</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.043605</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.048551</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.017588</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000817</v>
       </c>
     </row>
     <row r="35">
@@ -1558,19 +1558,19 @@
         <v>0.390818</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>4.021814</v>
+        <v>4.051134</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2.933421</v>
+        <v>2.977026</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.195655</v>
+        <v>0.244206</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.017588</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000817</v>
       </c>
     </row>
     <row r="37">
@@ -1930,19 +1930,19 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.107048</v>
+        <v>0.07772800000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.081141</v>
+        <v>0.037536</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.090823</v>
+        <v>0.042272</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.023934</v>
+        <v>0.006346</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.009133</v>
+        <v>0.008316</v>
       </c>
     </row>
     <row r="49">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/SMP.xlsx
+++ b/output/pdf_financials_xlsx/SMP.xlsx
@@ -604,13 +604,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>2.2e-05</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>0.001001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>0.003695</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.945963</v>
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>2.2e-05</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.001001</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.003695</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>1.326589</v>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-2.2e-05</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.001001</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.003695</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-1.326589</v>
@@ -3612,10 +3612,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-2.2e-05</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>2.2e-05</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -9366,7 +9366,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
         <v>-2.2e-05</v>
       </c>
@@ -12114,7 +12118,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E135" s="5" t="n">
         <v>2.2e-05</v>
       </c>
